--- a/review/zebra-shift-medical-review.xlsx
+++ b/review/zebra-shift-medical-review.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cases'!$A$1:$AD$311</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pictures'!$A$1:$L$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pictures'!$A$1:$M$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Standards cross-match'!$A$1:$H$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +49,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF4F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3E4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE1C8"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,10 +142,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -514,7 +533,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1695450"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -539,7 +558,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1562100"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -564,7 +583,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1562100"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -589,7 +608,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1562100"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -614,7 +633,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1543050"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -639,7 +658,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1914525"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -664,7 +683,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="1562100"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -689,7 +708,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -714,7 +733,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -739,7 +758,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -764,7 +783,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -789,7 +808,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -814,7 +833,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -839,7 +858,7 @@
       <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="3152775"/>
+    <ext cx="5715000" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -864,7 +883,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2533650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -889,7 +908,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2371725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -914,7 +933,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2371725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -939,7 +958,7 @@
       <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2371725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -964,7 +983,7 @@
       <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2200275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -989,7 +1008,7 @@
       <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2809875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -1014,7 +1033,7 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="3238500" cy="2371725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -1039,7 +1058,7 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="2857500" cy="3124200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1064,7 +1083,7 @@
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="2857500" cy="3124200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1089,7 +1108,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="2857500" cy="3124200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1114,7 +1133,7 @@
       <row>36</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="2857500" cy="3124200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1139,7 +1158,7 @@
       <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2876550"/>
+    <ext cx="2857500" cy="3124200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1147,6 +1166,1106 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="3124200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="3124200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2038350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2200275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="1876425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="1876425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2038350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2038350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2533650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1449,7 +2568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1482,7 +2601,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>• Pictures: all 37 ECGs, blood gases, X-rays and slides as the player sees them, with the answer options and the explanation shown afterwards.</t>
+          <t>• Pictures: all 81 ECGs, blood gases, lab panels, X-rays, ultrasound scans and slides as the player sees them, with the answer options and the explanation shown afterwards.</t>
         </is>
       </c>
     </row>
@@ -1579,12 +2698,33 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• "Standards cross-match" lists every emergency in the five Indonesian specialist standards you sent and where it lives in the game. Green rows were added from those documents; red rows are not in the game yet, with the reason.</t>
+          <t>• Blue marks the latest round: the 44 new pictures on the Pictures sheet, and on the Cases sheet the "Shown as a picture first" cell of every case that gained a picture.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>• "Reviewer note" (orange) on the Pictures sheet says which values I added beyond what the case text states, and where a shared picture differs from a case report. Check those first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• ECGs and scans are drawn by the game, not taken from patients. Judge whether the pattern is convincing and correct, rather than exact millimetres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• "Standards cross-match" lists every emergency in the five Indonesian specialist standards you sent and where it lives in the game. Green rows were added from those documents; red rows are not in the game yet, with the reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>• "Specialty pool" shows which specialist sees the case. Generalist specialties (EM, GP, Internal Medicine, Anaesthesia, Pathology) see every pool. "False alarm" cases arrive as emergencies but are benign.</t>
         </is>
@@ -2293,9 +3433,9 @@
           <t>1. Ultrasound: gallstones, thickened wall, pericholecystic fluid</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Gallstones with a thick wall and fluid around the gallbladder: acute cholecystitis)</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -2713,9 +3853,9 @@
           <t>1. X-ray: soft tissue swelling, no fracture</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Microscopy (Needle-shaped, negatively birefringent crystals: gout)</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
@@ -3133,9 +4273,9 @@
           <t>1. Renal ultrasound: no hydronephrosis or stone</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Microscopy (White cell casts: infection or inflammation in the kidney itself)</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -4111,9 +5251,9 @@
           <t>1. Echo: normal function</t>
         </is>
       </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Atrial flutter with 2:1 block: sawtooth waves at 300 a minute)</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
@@ -4531,9 +5671,9 @@
           <t>1. Ultrasound: gallstones, normal gallbladder wall</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Gallstones with a normal, thin wall: biliary colic)</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -5653,9 +6793,9 @@
           <t>1. Chest X-ray: mildly enlarged heart</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S29" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Complete heart block: P waves and QRS complexes dissociated)</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -5933,9 +7073,9 @@
           <t>1. Compression ultrasound: non-compressible left popliteal vein</t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S31" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Vein does not compress and has echoes inside: deep vein thrombosis)</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -6775,9 +7915,9 @@
           <t>1. CT head: no acute abnormality</t>
         </is>
       </c>
-      <c r="S37" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S37" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Lab panel (Very high glucose and osmolality without ketoacidosis: hyperosmolar hyperglycaemic state)</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -8456,9 +9596,9 @@
           <t>1. Bedside echo: mild lateral wall hypokinesis</t>
         </is>
       </c>
-      <c r="S49" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S49" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Lateral ST depression and T-wave inversion: ischaemia (NSTEMI))</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -10841,9 +11981,9 @@
           <t>1. Chest X-ray: normal</t>
         </is>
       </c>
-      <c r="S66" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S66" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Regular narrow-complex tachycardia with no visible P waves: SVT (AVNRT))</t>
         </is>
       </c>
       <c r="T66" s="5" t="inlineStr">
@@ -13364,9 +14504,9 @@
           <t>1. Renal ultrasound: slightly enlarged, echogenic kidneys</t>
         </is>
       </c>
-      <c r="S84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S84" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Microscopy (Red cell casts: bleeding from the glomerulus)</t>
         </is>
       </c>
       <c r="T84" s="5" t="inlineStr">
@@ -14766,9 +15906,10 @@
           <t>1. Echo: large pericardial effusion with right ventricular diastolic collapse</t>
         </is>
       </c>
-      <c r="S94" s="5" t="inlineStr">
-        <is>
-          <t>Tests clue 1: 12-lead ECG (Low voltage with electrical alternans: think tamponade)</t>
+      <c r="S94" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Low voltage with electrical alternans: think tamponade)
+Imaging clue 1: Ultrasound (Large pericardial effusion with right ventricular collapse: tamponade)</t>
         </is>
       </c>
       <c r="T94" s="5" t="inlineStr">
@@ -15750,9 +16891,9 @@
           <t>1. Temporal artery ultrasound: halo sign</t>
         </is>
       </c>
-      <c r="S101" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S101" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Dark halo around the temporal artery: giant cell arteritis)</t>
         </is>
       </c>
       <c r="T101" s="8" t="inlineStr">
@@ -16450,9 +17591,9 @@
           <t>1. Ultrasound: "snowstorm" appearance with no fetus</t>
         </is>
       </c>
-      <c r="S106" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S106" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound ("Snowstorm" uterus with no fetus: complete hydatidiform mole)</t>
         </is>
       </c>
       <c r="T106" s="5" t="inlineStr">
@@ -16590,9 +17731,9 @@
           <t>1. Chest X-ray: right hilar mass</t>
         </is>
       </c>
-      <c r="S107" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S107" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: 12-lead ECG (Short QT interval: hypercalcaemia)</t>
         </is>
       </c>
       <c r="T107" s="8" t="inlineStr">
@@ -17012,9 +18153,9 @@
           <t>1. Ultrasound: pyloric muscle 5 mm thick and 20 mm long</t>
         </is>
       </c>
-      <c r="S110" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S110" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Thick, long pyloric muscle: hypertrophic pyloric stenosis)</t>
         </is>
       </c>
       <c r="T110" s="5" t="inlineStr">
@@ -17993,9 +19134,9 @@
           <t>1. Ultrasound: target sign</t>
         </is>
       </c>
-      <c r="S117" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S117" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Target sign: intussusception)</t>
         </is>
       </c>
       <c r="T117" s="8" t="inlineStr">
@@ -20378,9 +21519,9 @@
           <t>1. FAST: free fluid in the left upper quadrant</t>
         </is>
       </c>
-      <c r="S134" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S134" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Free fluid around the spleen: a positive FAST)</t>
         </is>
       </c>
       <c r="T134" s="5" t="inlineStr">
@@ -22204,9 +23345,9 @@
           <t>1. Renal ultrasound: normal kidneys, no obstruction</t>
         </is>
       </c>
-      <c r="S147" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S147" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Lab panel (Dipstick blood with no red cells on microscopy: myoglobinuria)</t>
         </is>
       </c>
       <c r="T147" s="8" t="inlineStr">
@@ -22484,9 +23625,9 @@
           <t>1. Bedside ultrasound: 7.5 cm abdominal aortic aneurysm</t>
         </is>
       </c>
-      <c r="S149" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S149" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Abdominal aortic aneurysm with mural thrombus)</t>
         </is>
       </c>
       <c r="T149" s="8" t="inlineStr">
@@ -22626,9 +23767,9 @@
           <t>1. Transvaginal ultrasound: empty uterus, free fluid in the pouch of Douglas</t>
         </is>
       </c>
-      <c r="S150" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S150" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Empty uterus with free fluid in the pelvis: ruptured ectopic until proven otherwise)</t>
         </is>
       </c>
       <c r="T150" s="5" t="inlineStr">
@@ -22768,9 +23909,9 @@
           <t>1. Chest X-ray: clear</t>
         </is>
       </c>
-      <c r="S151" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S151" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Blood gas (Respiratory alkalosis plus a high anion gap metabolic acidosis: think salicylate)</t>
         </is>
       </c>
       <c r="T151" s="8" t="inlineStr">
@@ -23328,9 +24469,9 @@
           <t>1. Echo: aortic valve area 0.6 cm², mean gradient 56 mmHg</t>
         </is>
       </c>
-      <c r="S155" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S155" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Left ventricular hypertrophy with strain)</t>
         </is>
       </c>
       <c r="T155" s="8" t="inlineStr">
@@ -24306,9 +25447,9 @@
           <t>1. CT head: blood in the basal cisterns</t>
         </is>
       </c>
-      <c r="S162" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S162" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: 12-lead ECG (Giant, deep T-wave inversion with a long QT: cerebral T waves)</t>
         </is>
       </c>
       <c r="T162" s="5" t="inlineStr">
@@ -24588,9 +25729,9 @@
           <t>1. Bedside ultrasound: absent lung sliding on the left</t>
         </is>
       </c>
-      <c r="S164" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S164" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Barcode (stratosphere) sign: no lung sliding, pneumothorax)</t>
         </is>
       </c>
       <c r="T164" s="5" t="inlineStr">
@@ -24728,9 +25869,9 @@
           <t>1. Doppler ultrasound: no blood flow to the left testis</t>
         </is>
       </c>
-      <c r="S165" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S165" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (No colour flow in an enlarged left testis: testicular torsion)</t>
         </is>
       </c>
       <c r="T165" s="8" t="inlineStr">
@@ -24870,9 +26011,9 @@
           <t>1. Thyroid ultrasound: diffusely enlarged, hypervascular gland</t>
         </is>
       </c>
-      <c r="S166" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S166" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: 12-lead ECG (Irregularly irregular with no P waves: AF with a fast rate)</t>
         </is>
       </c>
       <c r="T166" s="5" t="inlineStr">
@@ -25151,9 +26292,9 @@
           <t>1. Chest X-ray: no aspiration</t>
         </is>
       </c>
-      <c r="S168" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S168" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Sinus tachycardia, broad QRS and a tall terminal R in aVR: sodium-channel blockade)</t>
         </is>
       </c>
       <c r="T168" s="5" t="inlineStr">
@@ -25571,9 +26712,9 @@
           <t>1. Echo: old anterior scar, ejection fraction 30%</t>
         </is>
       </c>
-      <c r="S171" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S171" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Broad-complex tachycardia with AV dissociation: ventricular tachycardia)</t>
         </is>
       </c>
       <c r="T171" s="8" t="inlineStr">
@@ -25993,9 +27134,9 @@
           <t>1. Chest X-ray: no mediastinal mass</t>
         </is>
       </c>
-      <c r="S174" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S174" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Microscopy (Many blasts with scanty cytoplasm and no Auer rods: acute lymphoblastic leukaemia)</t>
         </is>
       </c>
       <c r="T174" s="5" t="inlineStr">
@@ -26275,9 +27416,9 @@
           <t>1. Echo: mitral regurgitation with valve thickening</t>
         </is>
       </c>
-      <c r="S176" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S176" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: 12-lead ECG (First-degree AV block: PR interval over 200 ms)</t>
         </is>
       </c>
       <c r="T176" s="5" t="inlineStr">
@@ -26415,9 +27556,9 @@
           <t>1. CT abdomen: small, atrophic adrenal glands</t>
         </is>
       </c>
-      <c r="S177" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S177" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Lab panel (Low sodium with high potassium: think adrenal insufficiency)</t>
         </is>
       </c>
       <c r="T177" s="8" t="inlineStr">
@@ -26975,9 +28116,9 @@
           <t>1. CT head: diffuse brain swelling</t>
         </is>
       </c>
-      <c r="S181" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S181" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Microscopy (Ring forms inside red cells, some doubled: P. falciparum)</t>
         </is>
       </c>
       <c r="T181" s="8" t="inlineStr">
@@ -28238,9 +29379,9 @@
           <t>1. CT head: no mass</t>
         </is>
       </c>
-      <c r="S190" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S190" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Microscopy (Encapsulated budding yeasts with clear halos: Cryptococcus)</t>
         </is>
       </c>
       <c r="T190" s="5" t="inlineStr">
@@ -29080,9 +30221,9 @@
           <t>1. CT head: normal</t>
         </is>
       </c>
-      <c r="S196" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S196" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Microscopy (Envelope-shaped calcium oxalate crystals)</t>
         </is>
       </c>
       <c r="T196" s="5" t="inlineStr">
@@ -29780,9 +30921,9 @@
           <t>1. Nerve conduction: demyelinating polyneuropathy; MRI spine normal</t>
         </is>
       </c>
-      <c r="S201" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S201" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Lab panel (High protein with a normal cell count (albuminocytological dissociation): Guillain–Barré)</t>
         </is>
       </c>
       <c r="T201" s="8" t="inlineStr">
@@ -29920,9 +31061,9 @@
           <t>1. Liver ultrasound: no haematoma</t>
         </is>
       </c>
-      <c r="S202" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S202" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Microscopy (Schistocytes (fragmented red cells) with very few platelets)</t>
         </is>
       </c>
       <c r="T202" s="5" t="inlineStr">
@@ -30060,9 +31201,9 @@
           <t>1. MRI: left temporal lobe hyperintensity</t>
         </is>
       </c>
-      <c r="S203" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S203" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Lab panel (Lymphocytes and red cells with a normal glucose: viral encephalitis, think HSV)</t>
         </is>
       </c>
       <c r="T203" s="8" t="inlineStr">
@@ -30200,9 +31341,9 @@
           <t>1. Echo: 2.6 cm thick septum with outflow obstruction</t>
         </is>
       </c>
-      <c r="S204" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S204" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Very large voltages with deep T-wave inversion: hypertrophic cardiomyopathy)</t>
         </is>
       </c>
       <c r="T204" s="5" t="inlineStr">
@@ -33844,9 +34985,9 @@
           <t>1. Echo: dilated right ventricle; estimated pulmonary pressure 85 mmHg</t>
         </is>
       </c>
-      <c r="S230" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S230" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: 12-lead ECG (Right axis deviation with right ventricular strain)</t>
         </is>
       </c>
       <c r="T230" s="5" t="inlineStr">
@@ -34547,9 +35688,9 @@
 2. CT: splenic laceration with active bleeding</t>
         </is>
       </c>
-      <c r="S235" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S235" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Free fluid around the spleen: a positive FAST)</t>
         </is>
       </c>
       <c r="T235" s="8" t="inlineStr">
@@ -35249,9 +36390,9 @@
           <t>1. Chest X-ray: small right basal consolidation</t>
         </is>
       </c>
-      <c r="S240" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S240" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Long QT, then polymorphic VT twisting around the baseline: torsades de pointes)</t>
         </is>
       </c>
       <c r="T240" s="5" t="inlineStr">
@@ -35812,9 +36953,9 @@
           <t>1. Renal ultrasound: no obstruction</t>
         </is>
       </c>
-      <c r="S244" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S244" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Lab panel (High potassium, phosphate and urate with low calcium: tumour lysis syndrome)</t>
         </is>
       </c>
       <c r="T244" s="5" t="inlineStr">
@@ -36931,9 +38072,9 @@
           <t>1. Ultrasound: single large abscess in the right lobe</t>
         </is>
       </c>
-      <c r="S252" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S252" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound (Single large dark lesion in the liver: liver abscess)</t>
         </is>
       </c>
       <c r="T252" s="5" t="inlineStr">
@@ -37773,9 +38914,9 @@
           <t>1. Lateral neck X-ray: airway narrowing</t>
         </is>
       </c>
-      <c r="S258" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S258" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: 12-lead ECG (First-degree AV block: PR interval over 200 ms)</t>
         </is>
       </c>
       <c r="T258" s="5" t="inlineStr">
@@ -38754,9 +39895,9 @@
           <t>1. Abdominal X-ray: radio-opaque flecks in the bowel; dense "lead lines" at the knee growth plates</t>
         </is>
       </c>
-      <c r="S265" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S265" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Microscopy (Small pale red cells with basophilic stippling: think lead)</t>
         </is>
       </c>
       <c r="T265" s="8" t="inlineStr">
@@ -41554,9 +42695,9 @@
           <t>1. ECG: U waves; no imaging needed</t>
         </is>
       </c>
-      <c r="S285" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S285" s="9" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: 12-lead ECG (Flat T waves and prominent U waves: hypokalaemia)</t>
         </is>
       </c>
       <c r="T285" s="8" t="inlineStr">
@@ -41834,9 +42975,9 @@
           <t>1. MRI: enhancement at the base of the brain with early hydrocephalus</t>
         </is>
       </c>
-      <c r="S287" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S287" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Lab panel (Lymphocytes, very high protein and very low glucose: tuberculous meningitis)</t>
         </is>
       </c>
       <c r="T287" s="8" t="inlineStr">
@@ -43234,9 +44375,9 @@
           <t>1. Echo: structurally normal heart</t>
         </is>
       </c>
-      <c r="S297" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S297" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 1: 12-lead ECG (Second-degree AV block, Mobitz I (Wenckebach))</t>
         </is>
       </c>
       <c r="T297" s="8" t="inlineStr">
@@ -44355,9 +45496,9 @@
           <t>1. CT head: diffuse cerebral oedema</t>
         </is>
       </c>
-      <c r="S305" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="S305" s="9" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Microscopy (Motile amoebic trophozoites in CSF: Naegleria fowleri)</t>
         </is>
       </c>
       <c r="T305" s="8" t="inlineStr">
@@ -45261,7 +46402,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 AC2 AC3 AC4 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC35 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AC52 AC53 AC54 AC55 AC56 AC57 AC58 AC59 AC60 AC61 AC62 AC63 AC64 AC65 AC66 AC67 AC68 AC69 AC70 AC71 AC72 AC73 AC74 AC75 AC76 AC77 AC78 AC79 AC80 AC81 AC82 AC83 AC84 AC85 AC86 AC87 AC88 AC89 AC90 AC91 AC92 AC93 AC94 AC95 AC96 AC97 AC98 AC99 AC100 AC101 AC102 AC103 AC104 AC105 AC106 AC107 AC108 AC109 AC110 AC111 AC112 AC113 AC114 AC115 AC116 AC117 AC118 AC119 AC120 AC121 AC122 AC123 AC124 AC125 AC126 AC127 AC128 AC129 AC130 AC131 AC132 AC133 AC134 AC135 AC136 AC137 AC138 AC139 AC140 AC141 AC142 AC143 AC144 AC145 AC146 AC147 AC148 AC149 AC150 AC151 AC152 AC153 AC154 AC155 AC156 AC157 AC158 AC159 AC160 AC161 AC162 AC163 AC164 AC165 AC166 AC167 AC168 AC169 AC170 AC171 AC172 AC173 AC174 AC175 AC176 AC177 AC178 AC179 AC180 AC181 AC182 AC183 AC184 AC185 AC186 AC187 AC188 AC189 AC190 AC191 AC192 AC193 AC194 AC195 AC196 AC197 AC198 AC199 AC200 AC201 AC202 AC203 AC204 AC205 AC206 AC207 AC208 AC209 AC210 AC211 AC212 AC213 AC214 AC215 AC216 AC217 AC218 AC219 AC220 AC221 AC222 AC223 AC224 AC225 AC226 AC227 AC228 AC229 AC230 AC231 AC232 AC233 AC234 AC235 AC236 AC237 AC238 AC239 AC240 AC241 AC242 AC243 AC244 AC245 AC246 AC247 AC248 AC249 AC250 AC251 AC252 AC253 AC254 AC255 AC256 AC257 AC258 AC259 AC260 AC261 AC262 AC263 AC264 AC265 AC266 AC267 AC268 AC269 AC270 AC271 AC272 AC273 AC274 AC275 AC276 AC277 AC278 AC279 AC280 AC281 AC282 AC283 AC284 AC285 AC286 AC287 AC288 AC289 AC290 AC291 AC292 AC293 AC294 AC295 AC296 AC297 AC298 AC299 AC300 AC301 AC302 AC303 AC304 AC305 AC306 AC307 AC308 AC309 AC310 AC311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 AC2 AC3 AC4 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC35 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AC52 AC53 AC54 AC55 AC56 AC57 AC58 AC59 AC60 AC61 AC62 AC63 AC64 AC65 AC66 AC67 AC68 AC69 AC70 AC71 AC72 AC73 AC74 AC75 AC76 AC77 AC78 AC79 AC80 AC81 AC82 AC83 AC84 AC85 AC86 AC87 AC88 AC89 AC90 AC91 AC92 AC93 AC94 AC95 AC96 AC97 AC98 AC99 AC100 AC101 AC102 AC103 AC104 AC105 AC106 AC107 AC108 AC109 AC110 AC111 AC112 AC113 AC114 AC115 AC116 AC117 AC118 AC119 AC120 AC121 AC122 AC123 AC124 AC125 AC126 AC127 AC128 AC129 AC130 AC131 AC132 AC133 AC134 AC135 AC136 AC137 AC138 AC139 AC140 AC141 AC142 AC143 AC144 AC145 AC146 AC147 AC148 AC149 AC150 AC151 AC152 AC153 AC154 AC155 AC156 AC157 AC158 AC159 AC160 AC161 AC162 AC163 AC164 AC165 AC166 AC167 AC168 AC169 AC170 AC171 AC172 AC173 AC174 AC175 AC176 AC177 AC178 AC179 AC180 AC181 AC182 AC183 AC184 AC185 AC186 AC187 AC188 AC189 AC190 AC191 AC192 AC193 AC194 AC195 AC196 AC197 AC198 AC199 AC200 AC201 AC202 AC203 AC204 AC205 AC206 AC207 AC208 AC209 AC210 AC211 AC212 AC213 AC214 AC215 AC216 AC217 AC218 AC219 AC220 AC221 AC222 AC223 AC224 AC225 AC226 AC227 AC228 AC229 AC230 AC231 AC232 AC233 AC234 AC235 AC236 AC237 AC238 AC239 AC240 AC241 AC242 AC243 AC244 AC245 AC246 AC247 AC248 AC249 AC250 AC251 AC252 AC253 AC254 AC255 AC256 AC257 AC258 AC259 AC260 AC261 AC262 AC263 AC264 AC265 AC266 AC267 AC268 AC269 AC270 AC271 AC272 AC273 AC274 AC275 AC276 AC277 AC278 AC279 AC280 AC281 AC282 AC283 AC284 AC285 AC286 AC287 AC288 AC289 AC290 AC291 AC292 AC293 AC294 AC295 AC296 AC297 AC298 AC299 AC300 AC301 AC302 AC303 AC304 AC305 AC306 AC307 AC308 AC309 AC310 AC311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Needs change"</formula1>
     </dataValidation>
   </dataValidations>
@@ -45275,7 +46416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -45288,8 +46429,9 @@
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -45345,10 +46487,15 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>Reviewer note</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Your correction</t>
         </is>
@@ -45402,7 +46549,8 @@
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="7" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr"/>
     </row>
     <row r="3" ht="228.5" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -45452,7 +46600,8 @@
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="7" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="228.5" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -45502,7 +46651,8 @@
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="7" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="228.5" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -45552,7 +46702,8 @@
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="228.5" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -45602,7 +46753,8 @@
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="228.5" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -45625,12 +46777,14 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Atrial Fibrillation with Fast Ventricular Rate</t>
+          <t>Atrial Fibrillation with Fast Ventricular Rate
+Thyroid Storm</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Tests clue 1: ECG: atrial fibrillation at 152, no ischaemia</t>
+          <t>Tests clue 1: ECG: atrial fibrillation at 152, no ischaemia
+Tests clue 2: ECG: atrial fibrillation at 164</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -45651,8 +46805,13 @@
           <t>No organised P waves, a wavy baseline and completely irregular R–R intervals: atrial fibrillation.</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Drawn at about 148/min. Now also used for Thyroid Storm, whose report says AF at 164.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="228.5" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -45702,7 +46861,8 @@
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="228.5" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -45752,7 +46912,8 @@
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="228.5" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -45802,7 +46963,8 @@
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="228.5" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -45825,12 +46987,14 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Lyme Carditis</t>
+          <t>Lyme Carditis
+Complete Heart Block</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Tests clue 1: ECG: complete heart block</t>
+          <t>Tests clue 1: ECG: complete heart block
+Tests clue 1: ECG: P waves and QRS complexes march independently; broad escape rhythm</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -45851,16 +47015,21 @@
           <t>P waves march through at their own rate with no fixed relation to the slow, regular QRS complexes: third-degree (complete) heart block.</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Existing Lyme carditis picture, now also used for Complete Heart Block.</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="228.5" customHeight="1">
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>alternans</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>flutter</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -45875,1347 +47044,3682 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Cardiac Tamponade</t>
+          <t>Atrial Flutter</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Tests clue 1: ECG: low voltage with electrical alternans</t>
+          <t>Tests clue 1: ECG: sawtooth flutter waves in II, III and aVF with 2:1 block</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
+          <t>Atrial flutter with 2:1 block: sawtooth waves at 300 a minute</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>• Atrial fibrillation
+• Sinus tachycardia
+• AV nodal re-entry tachycardia</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Regular sawtooth flutter waves at 300 a minute, best seen in II, III and aVF, with every second one conducted: a ventricular rate of exactly 150. A regular rate of 150 should always make you look for flutter.</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="228.5" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>svt</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Supraventricular Tachycardia</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: regular narrow-complex tachycardia, no visible P waves</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Regular narrow-complex tachycardia with no visible P waves: SVT (AVNRT)</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>• Sinus tachycardia
+• Atrial fibrillation
+• Ventricular tachycardia</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>A fast, perfectly regular rhythm with narrow QRS complexes and no P waves before them: re-entry through the AV node. Try vagal manoeuvres, then adenosine.</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="228.5" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>vt</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Ventricular Tachycardia</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: broad-complex tachycardia, AV dissociation, fusion beats</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Broad-complex tachycardia with AV dissociation: ventricular tachycardia</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>• SVT with bundle branch block
+• Sinus tachycardia
+• Atrial flutter</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Regular, very broad complexes at about 170 a minute, with P waves marching through at their own slower rate: AV dissociation proves the rhythm comes from the ventricle. Treat a broad, regular tachycardia as VT.</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="228.5" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>tca</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Tricyclic Antidepressant Overdose</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: broad QRS of 140 ms with a tall R wave in aVR</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Sinus tachycardia, broad QRS and a tall terminal R in aVR: sodium-channel blockade</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>• Hyperkalaemia
+• Right bundle branch block only
+• Brugada pattern</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>A tachycardia with a QRS over 100 ms, a tall late R wave in aVR and a deep S in I: sodium channels are blocked, classically by a tricyclic. Give sodium bicarbonate.</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="228.5" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>tdp</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Torsades de Pointes</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: QTc 610 ms; runs of polymorphic VT twisting around the baseline</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Long QT, then polymorphic VT twisting around the baseline: torsades de pointes</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>• Ventricular fibrillation
+• Monomorphic VT
+• Atrial fibrillation with bundle branch block</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>The first beats have a very long QT. Then broad complexes run at about 250 a minute, their height swelling and shrinking so they seem to twist around the line. Give IV magnesium.</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="228.5" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>wenck</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Grayanotoxin (Mad Honey) Poisoning</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: sinus bradycardia with second-degree AV block</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Second-degree AV block, Mobitz I (Wenckebach)</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>• Mobitz II block
+• Complete heart block
+• Sinus arrhythmia</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>The PR interval gets longer with each beat until a P wave is not followed by a QRS, then the cycle starts again. Usually at the AV node, often from vagal tone or drugs, and rarely dangerous on its own.</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="228.5" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>firstdeg</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Acute Rheumatic Fever
+Diphtheria</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: ECG: prolonged PR interval
+Tests clue 2: ECG: first-degree heart block (myocarditis)</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>First-degree AV block: PR interval over 200 ms</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>• Mobitz I (Wenckebach)
+• Complete heart block
+• Normal sinus rhythm</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Every P wave is conducted, but each one sits far from its QRS: a fixed PR interval of about 340 ms. Look for the cause: carditis, drugs that slow the AV node, or high vagal tone.</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>Drawn at 64/min with a PR of about 340 ms, and used for both Acute Rheumatic Fever and Diphtheria.</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="228.5" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>cerebralt</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Subarachnoid Haemorrhage</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: ECG: deep symmetrical T-wave inversion</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Giant, deep T-wave inversion with a long QT: cerebral T waves</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>• Wellens pattern
+• Hyperkalaemia
+• Normal ECG</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Wide, deep T-wave inversion across many leads with a very long QT. With a sudden severe headache this is the brain talking to the heart, as in subarachnoid haemorrhage.</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Drawn widespread with a long QT; the case report says "deep symmetrical T-wave inversion".</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="228.5" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>nstemi</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Non-ST-Elevation Myocardial Infarction</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: ST depression and T-wave inversion in V4–V6</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Lateral ST depression and T-wave inversion: ischaemia (NSTEMI)</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>• Lateral STEMI
+• Digoxin effect
+• Normal ECG</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Flat or down-sloping ST depression with T-wave inversion in V4–V6, I and aVL. With chest pain and a rising troponin that is a non-ST-elevation MI.</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="228.5" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>lvh</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Severe Aortic Stenosis</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: left ventricular hypertrophy with strain</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Left ventricular hypertrophy with strain</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>• Lateral STEMI
+• Left bundle branch block
+• Normal ECG</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Huge voltages (a deep S in V1–V2 and a tall R in V5–V6) with asymmetrical ST depression and T inversion in the lateral leads: a thick, pressure-loaded left ventricle, as in aortic stenosis or long-standing high blood pressure.</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="228.5" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>hcm</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Hypertrophic Cardiomyopathy</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: very large voltages with deep T-wave inversion</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Very large voltages with deep T-wave inversion: hypertrophic cardiomyopathy</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>• Anterior STEMI
+• Wellens pattern
+• Normal athlete's ECG</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Massive QRS voltages with deep, symmetrical T-wave inversion across the chest leads in a young person who fainted on exertion: think hypertrophic cardiomyopathy and get an echo.</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="228.5" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>rvstrain</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Pulmonary Arterial Hypertension Crisis</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: ECG: right axis deviation and right ventricular strain</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Right axis deviation with right ventricular strain</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>• Left ventricular hypertrophy
+• Anterior STEMI
+• Normal ECG</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>A dominant R wave in V1, a deep S in I with a tall R in III (right axis), and T inversion over the right chest leads: the right ventricle is thick and pressure-loaded.</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="228.5" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>hypok</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Thyrotoxic Periodic Paralysis</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: ECG: U waves; no imaging needed</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Flat T waves and prominent U waves: hypokalaemia</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>• Hyperkalaemia
+• Long QT from drugs
+• Normal ECG</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Small, flat T waves with a separate rounded U wave after them, best seen in V2–V3, and slight ST depression: a very low potassium.</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="228.5" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>shortqt</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Hypercalcaemia of Malignancy</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: ECG: short QT</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Short QT interval: hypercalcaemia</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>• Long QT: hypocalcaemia
+• Hyperkalaemia
+• Normal ECG</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>The T wave follows the QRS almost at once, with hardly any ST segment, so the QT is short. With confusion, thirst and constipation, check the calcium.</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="228.5" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>alternans</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Cardiac Tamponade</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: ECG: low voltage with electrical alternans</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>Low voltage with electrical alternans: think tamponade</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>• Atrial fibrillation
 • Pericarditis without effusion
 • Normal ECG with lead artefact</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Small complexes whose height alternates beat to beat, with a tachycardia: the heart is swinging in a large effusion.</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="141.5" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="207.5" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>dka</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Diabetic Ketoacidosis</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Tests clue 2: VBG pH 7.08, bicarbonate 7, anion gap 26</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>High anion gap metabolic acidosis with respiratory compensation</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>• Normal anion gap metabolic acidosis
 • Acute respiratory acidosis
 • Metabolic alkalosis</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>pH low, bicarbonate very low, CO₂ blown off. Anion gap = 134 − (101 + 7) = 26: a raised gap, here from ketones.</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="131" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="194.75" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>copd</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>COPD Exacerbation</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: ABG on air: pH 7.31, pCO₂ 7.9 kPa, HCO₃ 32</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Acute-on-chronic respiratory acidosis (raised bicarbonate)</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>• Acute respiratory acidosis, uncompensated
 • Metabolic acidosis
 • Respiratory alkalosis</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>High CO₂ with a low pH is respiratory acidosis. The bicarbonate is already high, so the kidneys have been compensating for a long time: acute on chronic. Target saturations 88–92%.</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="131" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="194.75" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>panic</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Panic Attack</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Tests clue 2: VBG: pH 7.51, pCO₂ 3.6 kPa (respiratory alkalosis)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Acute respiratory alkalosis</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>• Metabolic alkalosis
 • Respiratory acidosis
 • Mixed metabolic acidosis and respiratory alkalosis</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>High pH with a low CO₂ and a normal bicarbonate: acute respiratory alkalosis from over-breathing. Normal oxygen helps, but exclude PE and DKA first.</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="131" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="194.75" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>opioid</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Opioid Overdose</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: VBG: pCO₂ 9.8 kPa, pH 7.21</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Acute respiratory acidosis from hypoventilation</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>• Chronic compensated respiratory acidosis
 • Metabolic acidosis
 • Normal blood gas</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Very high CO₂, low pH and a near-normal bicarbonate: acute hypoventilation with no time to compensate. Pinpoint pupils complete the picture.</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="129.5" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="181.25" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>methb</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Methaemoglobinaemia</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: ABG: normal pO₂, methaemoglobin 32%</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Normal pO₂ with a saturation gap: methaemoglobinaemia</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>• Type 1 respiratory failure
 • Carbon monoxide poisoning
 • Type 2 respiratory failure</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>The pO₂ is high on oxygen, yet the pulse oximeter reads about 85%. Co-oximetry shows methaemoglobin 32%. Treat with methylene blue.</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="158.75" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="229.25" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>methanol</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Methanol Poisoning</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: pH 7.05, anion gap 32</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>High anion gap acidosis with a raised osmolal gap: toxic alcohol</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>• Diabetic ketoacidosis
 • Lactic acidosis from shock
 • Normal anion gap acidosis</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Anion gap = 141 − (104 + 5) = 32. Calculated osmolality 2×141 + 5.2 + 6.1 ≈ 293, so the osmolal gap is about 38. Glucose and lactate do not explain it: methanol or ethylene glycol.</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="131" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="194.75" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>cholera</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Blood gas</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Cholera</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: K 2.8; metabolic acidosis; creatinine 210</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Normal anion gap metabolic acidosis with hypokalaemia</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>• High anion gap metabolic acidosis
 • Metabolic alkalosis from vomiting
 • Respiratory acidosis</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Anion gap = 136 − (114 + 13) = 9, which is normal, with a high chloride and low potassium: bicarbonate lost in stool.</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="256.25" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="254" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>rll</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Chest X-ray (PA)</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Community-Acquired Pneumonia</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Chest X-ray: right lower lobe consolidation with air bronchograms</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Right lower lobe consolidation with air bronchograms</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>• Right pleural effusion
 • Right pneumothorax
 • Normal chest film</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>A fluffy white opacity in the right lower zone with dark branching air bronchograms inside it, and the right heart border still visible: lower lobe, not middle lobe.</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="256.25" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35" ht="254" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>apo</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Chest X-ray (AP, portable)</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Acute Pulmonary Oedema</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Chest X-ray: bat-wing shadowing, upper lobe diversion, effusions</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Pulmonary oedema: big heart, bat-wing shadowing, effusions</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>• Bilateral pneumonia
 • Normal chest film
 • Miliary tuberculosis</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Cardiomegaly, perihilar bat-wing haze, short horizontal Kerley B lines at the bases and blunted costophrenic angles: fluid overload.</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="256.25" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="254" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>cavity</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Chest X-ray (PA)</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Pulmonary Tuberculosis</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Chest X-ray: right upper lobe cavity</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Right upper lobe cavity</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>• Right upper lobe collapse
 • Pancoast tumour at the apex
 • Normal chest film</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>A thick-walled ring with a dark centre and patchy shadowing around it in the right upper zone: a cavity. In this story, tuberculosis.</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23" ht="256.25" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="254" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>medi</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Chest X-ray (PA)</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Inhalational Anthrax</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Chest X-ray: widened mediastinum with pleural effusions</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Widened mediastinum with pleural effusions</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>• Cardiomegaly
 • Normal chest film
 • Bilateral hilar lymphadenopathy only</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>The upper mediastinum is much wider than it should be, with fluid at both bases. In a sick patient: haemorrhagic mediastinitis or a dissection.</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24" ht="256.25" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="254" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>ptx</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Chest X-ray (PA)</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Primary Spontaneous Pneumothorax</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Chest X-ray: left pneumothorax with a visible lung edge</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Left pneumothorax: a visible lung edge with no markings beyond it</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>• Bullous emphysema
 • Normal chest film
 • Left pleural effusion</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>A thin white pleural line runs parallel to the chest wall, and outside it there are no lung markings at all. The trachea is central, so it is not under tension.</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="256.25" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="254" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>freeair</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Erect chest X-ray</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Perforated Peptic Ulcer</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Erect chest X-ray: free gas under the right hemidiaphragm</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Free gas under the right hemidiaphragm (pneumoperitoneum)</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>• Chilaiditi sign (bowel between liver and diaphragm)
 • Normal gastric bubble only
 • Right lower lobe pneumonia</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>A smooth dark crescent separating the right hemidiaphragm from the liver on an erect film: free intraperitoneal gas from a perforated viscus.</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="256.25" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="254" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>sbo</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>X-ray</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Abdominal X-ray (supine)</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Small Bowel Obstruction</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Imaging clue 1: Abdominal X-ray: dilated central small-bowel loops with valvulae conniventes</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Dilated central small-bowel loops with valvulae conniventes</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>• Large bowel obstruction with haustra
 • Sigmoid volvulus (coffee-bean sign)
 • Normal bowel gas pattern</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Several dilated, centrally placed loops stacked like a ladder, crossed by thin lines that go all the way across (valvulae conniventes): small bowel, not colon.</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="234.5" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="233" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>malaria</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Thin blood film, Giemsa ×100</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Falciparum Malaria</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Tests clue 1: Thick and thin films: 6% P. falciparum parasitaemia</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Falciparum Malaria
+Cerebral Malaria</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Thick and thin films: 6% P. falciparum parasitaemia
+Tests clue 1: Thick film: Plasmodium falciparum, 8% parasitaemia</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Ring forms inside red cells, some doubled: P. falciparum</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>• Howell–Jolly bodies
 • Normal blood film
 • Babesia (Maltese cross)</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Delicate rings with one or two chromatin dots, several cells infected and some with two rings, plus a banana-shaped gametocyte: falciparum malaria.</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="234.5" customHeight="1">
-      <c r="A28" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Existing thin-film picture, now also used for Cerebral Malaria, whose report says thick film.</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="233" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>schisto</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Blood film, Wright stain ×100</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Thrombotic Thrombocytopenic Purpura</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Tests clue 1: Platelets 12, Hb 78, schistocytes on smear</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Thrombotic Thrombocytopenic Purpura
+HELLP Syndrome</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Platelets 12, Hb 78, schistocytes on smear
+Tests clue 2: Blood film: fragmented red cells</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Schistocytes (fragmented red cells) with very few platelets</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>• Spherocytes
 • Target cells
 • Normal blood film</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Helmet and triangle-shaped red cell fragments and almost no platelets: a microangiopathic haemolytic anaemia, such as TTP.</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29" ht="234.5" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Existing TTP picture, now also used for HELLP. The explanation mentions TTP.</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="233" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>atypical</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Blood film, Wright stain ×100</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Infectious Mononucleosis</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: Monospot positive; atypical lymphocytes on the blood film</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>Large atypical (reactive) lymphocytes</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>• Myeloblasts with Auer rods
 • Hypersegmented neutrophils
 • Normal blood film</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Big lymphocytes with plenty of pale blue cytoplasm that hugs the neighbouring red cells: reactive (Downey) cells, typical of EBV.</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="234.5" customHeight="1">
-      <c r="A30" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="233" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>tryp</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Thin blood film, Giemsa ×100</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>African Trypanosomiasis</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: Blood film: trypanosomes</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Trypanosomes: wavy flagellated parasites between red cells</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>• Microfilariae
 • Spirochaetes (Borrelia)
 • Malaria gametocytes</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Slender, wavy extracellular parasites with an undulating membrane, a central nucleus and a free flagellum: trypomastigotes.</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="234.5" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="233" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>sickle</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Blood film, Wright stain ×100</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Sickle Cell Pain Crisis</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: Blood film: sickle cells, target cells and Howell–Jolly bodies; Hb 74 (baseline 78)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Sickle cells with target cells and Howell–Jolly bodies</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>• Schistocytes
 • Spherocytes
 • Normal blood film</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Crescent-shaped cells, target cells and small nuclear remnants (a sign of a non-working spleen): sickle cell disease.</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="234.5" customHeight="1">
-      <c r="A32" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="233" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>gramneg</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>CSF Gram stain ×100</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Meningococcal Meningitis</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>Tests clue 2: CSF Gram stain: gram-negative diplococci</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Gram-negative diplococci inside neutrophils</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>• Gram-positive diplococci
 • Gram-positive rods
 • Yeasts (Cryptococcus)</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Pink, kidney-bean pairs of cocci, many inside neutrophils: Neisseria meningitidis in CSF.</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="234.5" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="233" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>grampos</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Sputum Gram stain ×100</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Community-Acquired Pneumonia</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Tests clue 2: Sputum Gram stain: gram-positive diplococci</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Gram-positive lancet-shaped diplococci</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>• Gram-negative diplococci
 • Gram-positive cocci in clusters
 • Gram-negative rods</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Purple, pointed pairs of cocci among pus cells: Streptococcus pneumoniae.</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="234.5" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="233" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>afb</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Sputum Ziehl–Neelsen stain ×100</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Pulmonary Tuberculosis</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: Sputum smear: acid-fast bacilli</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Acid-fast bacilli: red rods on a blue background</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>• Gram-positive cocci in chains
 • Fungal hyphae
 • No organisms seen</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Slender, slightly beaded red rods on a blue counterstain in a Ziehl–Neelsen stain: mycobacteria.</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35" ht="234.5" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49" ht="233" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>ldbodies</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Bone marrow aspirate, Giemsa ×100</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Visceral Leishmaniasis</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Tests clue 2: Bone marrow: Leishman–Donovan bodies</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Macrophage packed with Leishman–Donovan bodies</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>• Megaloblastic changes
 • Gaucher cell
 • Histoplasma yeasts</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>A macrophage stuffed with tiny oval bodies, each with a nucleus and a small rod-like kinetoplast: Leishmania amastigotes. Histoplasma has no kinetoplast.</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36" ht="234.5" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="233" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>vibrio</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Stool dark-field microscopy</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Cholera</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>Tests clue 2: Stool dark-field: darting comma-shaped bacteria</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>Darting comma-shaped bacteria (Vibrio)</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>• Spirochaetes
 • Motile Giardia trophozoites
 • No organisms seen</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Bright, curved comma-shaped rods shooting across a dark-field slide: Vibrio cholerae.</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37" ht="234.5" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51" ht="233" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>boxcar</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Blood culture Gram stain ×100</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Inhalational Anthrax</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: Blood culture: large gram-positive rods in chains ("boxcars")</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Large gram-positive rods in chains ("boxcars")</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>• Gram-positive cocci in chains
 • Gram-negative rods
 • Branching gram-positive filaments</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Big, square-ended purple rods lined up end to end like railway carriages: Bacillus anthracis.</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38" ht="234.5" customHeight="1">
-      <c r="A38" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="233" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>bipolar</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Microscopy</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Node aspirate, Wayson stain ×100</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Bubonic Plague</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Tests clue 1: Node aspirate: bipolar-staining gram-negative coccobacilli</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Bipolar "safety-pin" coccobacilli</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>• Gram-positive diplococci
 • Spirochaetes
 • Yeast cells</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Small rods stained darker at both ends, like a closed safety pin: Yersinia pestis on a Wayson or Giemsa stain.</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53" ht="233" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>gout</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Joint fluid, polarised light</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Acute Gout</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Joint aspirate: needle-shaped, negatively birefringent crystals</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Needle-shaped, negatively birefringent crystals: gout</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>• Rhomboid, positively birefringent crystals: pseudogout
+• Gram-positive cocci: septic arthritis
+• No crystals seen</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Thin needles that glow yellow when they lie along the compensator axis and blue across it are negatively birefringent: monosodium urate. Pseudogout crystals are short rhomboids with the opposite colours.</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="233" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>oxalate</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Urine microscopy ×40</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Ethylene Glycol Poisoning</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Urine microscopy: envelope-shaped calcium oxalate crystals</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Envelope-shaped calcium oxalate crystals</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>• Coffin-lid triple phosphate crystals
+• Hexagonal cystine crystals
+• No crystals seen</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Square crystals with an X across them, like the back of an envelope: calcium oxalate dihydrate. With a high anion gap and a high osmolal gap, think ethylene glycol.</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55" ht="233" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>rbccast</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Urine microscopy ×40</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Acute Post-Streptococcal Glomerulonephritis</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Urinalysis: blood 3+, red cell casts, protein 1+</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Red cell casts: bleeding from the glomerulus</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>• White cell casts
+• Hyaline casts only
+• Free red cells from the bladder</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>A cylinder moulded in a kidney tubule and packed with red cells. Red cells can only get into a cast inside the nephron, so this means glomerulonephritis.</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="233" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>wbccast</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Urine microscopy ×40</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Acute Pyelonephritis</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Urinalysis: nitrite +, leukocyte esterase +, white cell casts</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>White cell casts: infection or inflammation in the kidney itself</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>• Red cell casts
+• Hyaline casts only
+• Bacteria without casts (cystitis)</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>A tubular cast full of white cells puts the inflammation inside the kidney, so with fever and loin pain this is pyelonephritis rather than a simple bladder infection.</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57" ht="233" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>indiaink</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>CSF India ink preparation ×40</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Cryptococcal Meningitis</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: CSF: opening pressure 36 cmH₂O, India ink positive</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Encapsulated budding yeasts with clear halos: Cryptococcus</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>• Red cells only
+• Candida with pseudohyphae
+• Toxoplasma cysts</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Round yeasts, some budding, each surrounded by a clear halo where the thick capsule keeps the ink away: Cryptococcus neoformans.</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58" ht="233" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>stippling</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Blood film, Wright stain ×100</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Lead Poisoning</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Blood film: microcytic anaemia with basophilic stippling</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Small pale red cells with basophilic stippling: think lead</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>• Target cells of thalassaemia
+• Howell–Jolly bodies
+• Malaria parasites</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Small, pale (microcytic, hypochromic) red cells with fine blue dots scattered through them: leftover RNA because lead blocks the enzyme that clears it.</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59" ht="233" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>blasts</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Blood film, Wright stain ×100</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Acute Lymphoblastic Leukaemia</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Blood film: many lymphoblasts</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Many blasts with scanty cytoplasm and no Auer rods: acute lymphoblastic leukaemia</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>• Myeloblasts with Auer rods (AML)
+• Reactive lymphocytes (glandular fever)
+• Smear cells (CLL)</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Large cells with a high nucleus-to-cytoplasm ratio, fine chromatin and nucleoli crowd out the normal cells. No Auer rods, and in a child this is most likely ALL.</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60" ht="233" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>naegleria</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>CSF wet mount ×40</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Primary Amoebic Meningoencephalitis</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: CSF wet mount: motile trophozoites</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Motile amoebic trophozoites in CSF: Naegleria fowleri</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>• White cells only (bacterial meningitis)
+• Cryptococcus
+• Red cells from a traumatic tap</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Shape-shifting cells pushing out blunt pseudopods, each with a nucleus holding a big central dot (karyosome): free-living amoebae. After warm freshwater swimming this is primary amoebic meningoencephalitis.</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61" ht="221.75" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Bedside ultrasound</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Ruptured Abdominal Aortic Aneurysm</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Bedside ultrasound: 7.5 cm abdominal aortic aneurysm</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Abdominal aortic aneurysm with mural thrombus</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>• Normal aorta
+• Retroperitoneal lymph nodes
+• Dilated inferior vena cava</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>A round aorta measuring 7.5 cm from outer wall to outer wall (normal is under 3 cm), lined with grey thrombus. In a shocked patient with back pain, assume rupture and call the vascular surgeons.</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62" ht="221.75" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>chole</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>RUQ ultrasound</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Acute Cholecystitis</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound: gallstones, thickened wall, pericholecystic fluid</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Gallstones with a thick wall and fluid around the gallbladder: acute cholecystitis</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>• Gallstones with a normal wall: biliary colic
+• Gallbladder polyp
+• Normal gallbladder</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Bright stones with dark acoustic shadows, a gallbladder wall thicker than 3 mm and a rim of fluid around it. With a sonographic Murphy sign this is acute cholecystitis.</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63" ht="221.75" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>gstones</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>RUQ ultrasound</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Biliary Colic</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound: gallstones, normal gallbladder wall</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Gallstones with a normal, thin wall: biliary colic</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>• Acute cholecystitis
+• Gallbladder polyp
+• Normal gallbladder</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Bright, mobile stones casting dark shadows, but the wall is thin and there is no fluid around it: stones without inflammation.</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="221.75" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>ectopic</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Pelvic ultrasound</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Ruptured Ectopic Pregnancy</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Transvaginal ultrasound: empty uterus, free fluid in the pouch of Douglas</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Empty uterus with free fluid in the pelvis: ruptured ectopic until proven otherwise</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>• Early intrauterine pregnancy
+• Normal pelvis
+• Ovarian cyst</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>No gestational sac in the uterus, only a thin bright endometrial line, and black free fluid with grey clot behind it. With a positive pregnancy test this is a ruptured ectopic.</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65" ht="221.75" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Abdominal ultrasound</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Intussusception</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound: target sign</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Target sign: intussusception</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>• Normal bowel loop
+• Appendicitis
+• Lymph node</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Rings within rings, about 3 cm across: bowel telescoped into bowel, with a crescent of trapped mesenteric fat. In a toddler with colicky pain this is intussusception.</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66" ht="221.75" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>pyloric</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Abdominal ultrasound</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Hypertrophic Pyloric Stenosis</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound: pyloric muscle 5 mm thick and 20 mm long</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Thick, long pyloric muscle: hypertrophic pyloric stenosis</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>• Normal pylorus
+• Duodenal atresia
+• Gastric outlet tumour</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Pyloric muscle 5 mm thick (over 3 mm is abnormal) and channel 20 mm long (over 15 mm is abnormal), with stomach contents stuck behind it.</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67" ht="221.75" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>mole</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Pelvic ultrasound</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Hydatidiform Mole</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound: "snowstorm" appearance with no fetus</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>"Snowstorm" uterus with no fetus: complete hydatidiform mole</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>• Missed miscarriage
+• Twin pregnancy
+• Uterine fibroids</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>An enlarged uterus filled with echogenic tissue riddled with tiny cysts and no fetus. With a very high hCG this is a complete molar pregnancy.</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68" ht="221.75" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>FAST scan</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Splenic Rupture
+Penetrating Abdominal Trauma</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: FAST scan: free fluid around the spleen
+Imaging clue 1: FAST: free fluid in the left upper quadrant</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Free fluid around the spleen: a positive FAST</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>• Normal left upper quadrant
+• Pleural effusion only
+• Kidney stone</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Black fluid between the spleen and kidney and above the spleen. After trauma, free fluid means blood until proven otherwise; an unstable patient goes to theatre.</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69" ht="221.75" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>dvt</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Compression ultrasound</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Deep Vein Thrombosis</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Compression ultrasound: non-compressible left popliteal vein</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Vein does not compress and has echoes inside: deep vein thrombosis</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>• Normal compressible vein
+• Baker's cyst
+• Arterial aneurysm</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Pressing with the probe should flatten a normal vein completely. This one stays round and is full of grey echoes, while the artery beside it is unchanged: a popliteal DVT.</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70" ht="221.75" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>lungm</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Lung ultrasound</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Tension Pneumothorax</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Bedside ultrasound: absent lung sliding on the left</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Barcode (stratosphere) sign: no lung sliding, pneumothorax</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>• Seashore sign: normal lung sliding
+• B-lines: interstitial fluid
+• Pleural effusion</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>On M-mode, normal lung below the pleural line looks grainy like sand (the seashore). Here everything is flat horizontal lines, top to bottom: no sliding, so air separates the pleura.</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>The case report says "absent lung sliding"; the picture shows the M-mode barcode sign.</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71" ht="221.75" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>torsion</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Scrotal Doppler ultrasound</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Testicular Torsion</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Doppler ultrasound: no blood flow to the left testis</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>No colour flow in an enlarged left testis: testicular torsion</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>• Epididymo-orchitis
+• Normal testes
+• Hydrocele</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Colour Doppler shows flow in the right testis but none in the swollen, slightly patchy left one. Do not wait for imaging if you suspect torsion: the clock is ticking.</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
+      <c r="L71" s="5" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="221.75" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>halo</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Temporal artery ultrasound</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Giant Cell Arteritis</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Temporal artery ultrasound: halo sign</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Dark halo around the temporal artery: giant cell arteritis</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>• Normal temporal artery
+• Temporal artery aneurysm
+• Atherosclerotic plaque</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>A dark, even ring of swollen wall around the artery in both views. It does not compress away. With jaw pain and a high ESR this is giant cell arteritis: start steroids now.</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73" ht="221.75" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>tamp</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Bedside echo</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Cardiac Tamponade</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Echo: large pericardial effusion with right ventricular diastolic collapse</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Large pericardial effusion with right ventricular collapse: tamponade</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>• Pleural effusion
+• Dilated cardiomyopathy
+• Normal heart</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>A wide black rim of fluid all around the heart, and the right ventricle is squashed flat in diastole. In a shocked patient this needs drainage now.</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Second picture for Cardiac Tamponade, on top of the existing electrical alternans ECG.</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74" ht="221.75" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>abscess</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Liver ultrasound</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Amoebic Liver Abscess</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Imaging clue 1: Ultrasound: single large abscess in the right lobe</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Single large dark lesion in the liver: liver abscess</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>• Simple liver cyst
+• Haemangioma
+• Normal liver</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>A round, dark lesion with low-level echoes inside, a thick wall and brighter tissue behind it. With fever and right upper quadrant pain after travel, think amoebic liver abscess.</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75" ht="168.5" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>gbs</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>CSF analysis</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Guillain–Barré Syndrome</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: CSF: protein 1.8 g/L with normal cell count</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>High protein with a normal cell count (albuminocytological dissociation): Guillain–Barré</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>• Bacterial meningitis
+• Viral meningitis
+• Tuberculous meningitis</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>The protein is four times the upper limit, yet there are almost no white cells and the glucose is normal. That split is typical of Guillain–Barré a week or more into the weakness.</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>Only the protein (1.8 g/L) and the normal cell count come from the case. The other CSF values are mine.</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="181.25" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>tbm</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>CSF analysis</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Tuberculous Meningitis</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: CSF: lymphocytes, protein 3.2 g/L, very low glucose</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Lymphocytes, very high protein and very low glucose: tuberculous meningitis</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>• Bacterial meningitis
+• Viral meningitis
+• Guillain–Barré syndrome</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Hundreds of white cells, mostly lymphocytes, a protein above 3 g/L and a glucose under a fifth of the blood level, with no organisms on Gram stain. Weeks of headache make TB the answer.</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>Lymphocytes, protein 3.2 g/L and a very low glucose come from the case. The cell count, glucose value, ADA and opening pressure are mine.</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77" ht="221.75" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>hsvcsf</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>CSF analysis</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>HSV Encephalitis</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: CSF: lymphocytes, red cells, raised protein, normal glucose</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Lymphocytes and red cells with a normal glucose: viral encephalitis, think HSV</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>• Bacterial meningitis
+• A traumatic tap only
+• Tuberculous meningitis</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>A lymphocytic CSF with a normal glucose points to a virus. Red cells that do not clear from tube 1 to tube 3 fit the bleeding, necrotising temporal lobe of HSV. Start aciclovir without waiting for the PCR.</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>The case says lymphocytes, red cells, raised protein and normal glucose. All the numbers, including the tube 1 and tube 3 red cell counts, are mine.</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78" ht="155.75" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>addison</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Electrolytes</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Addisonian Crisis</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Na 124, K 6.1 mmol/L</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Low sodium with high potassium: think adrenal insufficiency</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>• SIADH
+• Pseudohyperkalaemia
+• Chronic kidney disease</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Hyponatraemia together with hyperkalaemia, a raised urea from dehydration and a mild acidosis: the pattern of missing aldosterone and cortisol. In a shocked patient give hydrocortisone straight away.</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>Na 124 and K 6.1 come from the case. Chloride, bicarbonate, urea and creatinine are mine.</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79" ht="155.75" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>tls</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Electrolytes and urate</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Tumour Lysis Syndrome</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Potassium 6.9, phosphate 3.1, urate 0.89, calcium 1.7 mmol/L</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>High potassium, phosphate and urate with low calcium: tumour lysis syndrome</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>• Rhabdomyolysis
+• Primary hyperparathyroidism
+• Normal results</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Dying tumour cells release potassium, phosphate and nucleic acids (urate); phosphate then binds calcium. The CK is normal, so this is not muscle breakdown.</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>K, phosphate, urate and calcium come from the case. LDH and CK are mine (CK is there to rule out rhabdomyolysis).</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80" ht="168.5" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>rhabdo</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Urinalysis</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Rhabdomyolysis</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Dipstick: blood 3+ but no red cells on microscopy; creatinine 162 µmol/L</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Dipstick blood with no red cells on microscopy: myoglobinuria</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>• Glomerulonephritis
+• Urinary tract infection
+• Kidney stone</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>The dipstick reacts to the haem in myoglobin as well as in red cells. Strongly positive blood with no red cells under the microscope, in dark urine, means muscle breakdown.</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>Blood 3+ with no red cells comes from the case. Colour, protein and casts are mine.</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81" ht="168.5" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>hhs</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Lab panel</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Glucose, osmolality and ketones</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Hyperosmolar Hyperglycaemic State</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 2: Ketones 0.8 mmol/L; pH 7.34, bicarbonate 20 mmol/L</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Very high glucose and osmolality without ketoacidosis: hyperosmolar hyperglycaemic state</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>• Diabetic ketoacidosis
+• Hypoglycaemia
+• Diabetes insipidus</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>A glucose of 48 and an osmolality over 320, but ketones under 3 and a near-normal pH and bicarbonate. Rehydrate slowly; this is not DKA.</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>Glucose, osmolality, ketones, pH and bicarbonate come from the case. Sodium and urea are mine.</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82" ht="207.5" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>salicylate</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Blood gas</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Blood gas</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Salicylate Overdose</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Tests clue 1: Blood gas: respiratory alkalosis plus a high anion-gap metabolic acidosis</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Respiratory alkalosis plus a high anion gap metabolic acidosis: think salicylate</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>• Pure respiratory alkalosis
+• Diabetic ketoacidosis
+• Normal blood gas</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>The pH is near normal, but the CO₂ is far too low and so is the bicarbonate. Anion gap = 140 − (104 + 14) = 22. Two primary disorders at once, with tinnitus and over-breathing: aspirin.</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Every value is mine. The case only says respiratory alkalosis plus a high anion gap acidosis.</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
-  <conditionalFormatting sqref="K2:K38">
+  <autoFilter ref="A1:M82"/>
+  <conditionalFormatting sqref="L2:L82">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>K2="Needs change"</formula>
+      <formula>L2="Needs change"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>K2="OK"</formula>
+      <formula>L2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 AC2 AC3 AC4 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC35 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AC52 AC53 AC54 AC55 AC56 AC57 AC58 AC59 AC60 AC61 AC62 AC63 AC64 AC65 AC66 AC67 AC68 AC69 AC70 AC71 AC72 AC73 AC74 AC75 AC76 AC77 AC78 AC79 AC80 AC81 AC82 AC83 AC84 AC85 AC86 AC87 AC88 AC89 AC90 AC91 AC92 AC93 AC94 AC95 AC96 AC97 AC98 AC99 AC100 AC101 AC102 AC103 AC104 AC105 AC106 AC107 AC108 AC109 AC110 AC111 AC112 AC113 AC114 AC115 AC116 AC117 AC118 AC119 AC120 AC121 AC122 AC123 AC124 AC125 AC126 AC127 AC128 AC129 AC130 AC131 AC132 AC133 AC134 AC135 AC136 AC137 AC138 AC139 AC140 AC141 AC142 AC143 AC144 AC145 AC146 AC147 AC148 AC149 AC150 AC151 AC152 AC153 AC154 AC155 AC156 AC157 AC158 AC159 AC160 AC161 AC162 AC163 AC164 AC165 AC166 AC167 AC168 AC169 AC170 AC171 AC172 AC173 AC174 AC175 AC176 AC177 AC178 AC179 AC180 AC181 AC182 AC183 AC184 AC185 AC186 AC187 AC188 AC189 AC190 AC191 AC192 AC193 AC194 AC195 AC196 AC197 AC198 AC199 AC200 AC201 AC202 AC203 AC204 AC205 AC206 AC207 AC208 AC209 AC210 AC211 AC212 AC213 AC214 AC215 AC216 AC217 AC218 AC219 AC220 AC221 AC222 AC223 AC224 AC225 AC226 AC227 AC228 AC229 AC230 AC231 AC232 AC233 AC234 AC235 AC236 AC237 AC238 AC239 AC240 AC241 AC242 AC243 AC244 AC245 AC246 AC247 AC248 AC249 AC250 AC251 AC252 AC253 AC254 AC255 AC256 AC257 AC258 AC259 AC260 AC261 AC262 AC263 AC264 AC265 AC266 AC267 AC268 AC269 AC270 AC271 AC272 AC273 AC274 AC275 AC276 AC277 AC278 AC279 AC280 AC281 AC282 AC283 AC284 AC285 AC286 AC287 AC288 AC289 AC290 AC291 AC292 AC293 AC294 AC295 AC296 AC297 AC298 AC299 AC300 AC301 AC302 AC303 AC304 AC305 AC306 AC307 AC308 AC309 AC310 AC311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 AC2 AC3 AC4 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC35 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AC52 AC53 AC54 AC55 AC56 AC57 AC58 AC59 AC60 AC61 AC62 AC63 AC64 AC65 AC66 AC67 AC68 AC69 AC70 AC71 AC72 AC73 AC74 AC75 AC76 AC77 AC78 AC79 AC80 AC81 AC82 AC83 AC84 AC85 AC86 AC87 AC88 AC89 AC90 AC91 AC92 AC93 AC94 AC95 AC96 AC97 AC98 AC99 AC100 AC101 AC102 AC103 AC104 AC105 AC106 AC107 AC108 AC109 AC110 AC111 AC112 AC113 AC114 AC115 AC116 AC117 AC118 AC119 AC120 AC121 AC122 AC123 AC124 AC125 AC126 AC127 AC128 AC129 AC130 AC131 AC132 AC133 AC134 AC135 AC136 AC137 AC138 AC139 AC140 AC141 AC142 AC143 AC144 AC145 AC146 AC147 AC148 AC149 AC150 AC151 AC152 AC153 AC154 AC155 AC156 AC157 AC158 AC159 AC160 AC161 AC162 AC163 AC164 AC165 AC166 AC167 AC168 AC169 AC170 AC171 AC172 AC173 AC174 AC175 AC176 AC177 AC178 AC179 AC180 AC181 AC182 AC183 AC184 AC185 AC186 AC187 AC188 AC189 AC190 AC191 AC192 AC193 AC194 AC195 AC196 AC197 AC198 AC199 AC200 AC201 AC202 AC203 AC204 AC205 AC206 AC207 AC208 AC209 AC210 AC211 AC212 AC213 AC214 AC215 AC216 AC217 AC218 AC219 AC220 AC221 AC222 AC223 AC224 AC225 AC226 AC227 AC228 AC229 AC230 AC231 AC232 AC233 AC234 AC235 AC236 AC237 AC238 AC239 AC240 AC241 AC242 AC243 AC244 AC245 AC246 AC247 AC248 AC249 AC250 AC251 AC252 AC253 AC254 AC255 AC256 AC257 AC258 AC259 AC260 AC261 AC262 AC263 AC264 AC265 AC266 AC267 AC268 AC269 AC270 AC271 AC272 AC273 AC274 AC275 AC276 AC277 AC278 AC279 AC280 AC281 AC282 AC283 AC284 AC285 AC286 AC287 AC288 AC289 AC290 AC291 AC292 AC293 AC294 AC295 AC296 AC297 AC298 AC299 AC300 AC301 AC302 AC303 AC304 AC305 AC306 AC307 AC308 AC309 AC310 AC311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Needs change"</formula1>
     </dataValidation>
   </dataValidations>
@@ -47456,9 +50960,9 @@
           <t>Hypoglycaemia</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
@@ -47487,10 +50991,9 @@
 Salt-Wasting Congenital Adrenal Hyperplasia</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -47617,10 +51120,9 @@
 Critical Coarctation of the Aorta</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Paediatrics pool</t>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -47649,9 +51151,10 @@
 Status Epilepticus</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents
+Core game</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -47712,10 +51215,9 @@
 Malrotation with Midgut Volvulus</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -47775,10 +51277,9 @@
 Toxic Shock Syndrome</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -47839,10 +51340,9 @@
 Vitamin K Deficiency Bleeding</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -47903,9 +51403,10 @@
 Small Bowel Obstruction</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents
+Core game</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -47933,7 +51434,7 @@
           <t>Necrotising Enterocolitis</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -48059,9 +51560,10 @@
 Perforated Peptic Ulcer</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents
+Core game</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
@@ -48089,7 +51591,7 @@
           <t>Oesophageal Atresia with Tracheo-Oesophageal Fistula</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -48119,7 +51621,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -48184,10 +51686,9 @@
 Vitamin K Deficiency Bleeding</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Paediatrics pool</t>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
@@ -48338,10 +51839,9 @@
 Neonatal Tetanus</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
@@ -48399,9 +51899,9 @@
           <t>Toxic Shock Syndrome</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
@@ -48520,10 +52020,9 @@
 Cerebral Malaria</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
@@ -48641,9 +52140,9 @@
           <t>Rabies</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
@@ -48769,7 +52268,7 @@
           <t>Critical Coarctation of the Aorta</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -48799,9 +52298,9 @@
           <t>Tetralogy of Fallot Hypercyanotic Spell</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Paediatrics pool</t>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
@@ -48923,7 +52422,7 @@
           <t>Pulmonary Arterial Hypertension Crisis</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49014,9 +52513,9 @@
 Acute Post-Streptococcal Glomerulonephritis</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Cardiology pool
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents
 Paediatrics pool</t>
         </is>
       </c>
@@ -49046,10 +52545,9 @@
 Djenkol Bean Poisoning</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
@@ -49107,7 +52605,7 @@
           <t>Djenkol Bean Poisoning</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49139,7 +52637,7 @@
 Salt-Wasting Congenital Adrenal Hyperplasia</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49169,7 +52667,7 @@
           <t>Neonatal Sepsis</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49199,7 +52697,7 @@
           <t>Neonatal Tetanus</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49229,7 +52727,7 @@
           <t>Vitamin K Deficiency Bleeding</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49259,7 +52757,7 @@
           <t>Acute Bilirubin Encephalopathy</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49289,7 +52787,7 @@
           <t>Congenital Diaphragmatic Hernia</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49319,7 +52817,7 @@
           <t>Malrotation with Midgut Volvulus</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49349,7 +52847,7 @@
           <t>Hypertrophic Pyloric Stenosis</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49379,7 +52877,7 @@
           <t>Necrotising Enterocolitis</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49409,7 +52907,7 @@
           <t>Salt-Wasting Congenital Adrenal Hyperplasia</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49439,7 +52937,7 @@
           <t>Maple Syrup Urine Disease Crisis</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49469,7 +52967,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -49503,7 +53001,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -49537,7 +53035,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -49573,9 +53071,10 @@
 Japanese Encephalitis</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents
+Core game</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
@@ -49603,9 +53102,9 @@
           <t>Status Epilepticus</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
@@ -49784,7 +53283,7 @@
           <t>Near Drowning</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49846,7 +53345,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -49880,7 +53379,7 @@
           <t>Non-Accidental Injury</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -49910,7 +53409,7 @@
           <t>Unstable Angina</t>
         </is>
       </c>
-      <c r="E86" s="9" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50189,7 +53688,7 @@
           <t>Pulmonary Arterial Hypertension Crisis</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50219,7 +53718,7 @@
           <t>Sick Sinus Syndrome</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50280,7 +53779,7 @@
           <t>Atrial Flutter</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50436,7 +53935,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E103" s="10" t="inlineStr">
+      <c r="E103" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -50501,7 +54000,7 @@
           <t>Traumatic Aortic Injury</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50655,7 +54154,7 @@
           <t>Cardiogenic Shock</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50685,9 +54184,9 @@
           <t>Hypertensive Emergency</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>Cardiology pool</t>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
@@ -50715,7 +54214,7 @@
           <t>Anticoagulant-Associated Bleeding</t>
         </is>
       </c>
-      <c r="E112" s="9" t="inlineStr">
+      <c r="E112" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50745,9 +54244,9 @@
           <t>Tetralogy of Fallot Hypercyanotic Spell</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>Paediatrics pool</t>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -50811,10 +54310,9 @@
 Chronic Subdural Haematoma</t>
         </is>
       </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
@@ -50842,7 +54340,7 @@
           <t>Traumatic Spinal Cord Injury</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -50938,10 +54436,9 @@
 Wernicke Encephalopathy</t>
         </is>
       </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr"/>
@@ -50969,9 +54466,9 @@
           <t>Status Epilepticus</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -51007,11 +54504,9 @@
 Transient Ischaemic Attack</t>
         </is>
       </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game
-Neurology pool</t>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
@@ -51075,9 +54570,10 @@
 Japanese Encephalitis</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents
+Core game</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr"/>
@@ -51140,7 +54636,7 @@
           <t>Cerebral Malaria</t>
         </is>
       </c>
-      <c r="E125" s="9" t="inlineStr">
+      <c r="E125" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -51170,9 +54666,9 @@
           <t>Rabies</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
@@ -51200,9 +54696,9 @@
           <t>Tetanus</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>Core game</t>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr"/>
@@ -51230,7 +54726,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E128" s="10" t="inlineStr">
+      <c r="E128" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -51328,9 +54824,9 @@
           <t>Posterior Reversible Encephalopathy Syndrome</t>
         </is>
       </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>Neurology pool</t>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr"/>
@@ -51492,10 +54988,9 @@
 Wernicke Encephalopathy</t>
         </is>
       </c>
-      <c r="E136" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr"/>
@@ -51651,10 +55146,9 @@
 Thyrotoxic Periodic Paralysis</t>
         </is>
       </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr"/>
@@ -51684,11 +55178,9 @@
 Acute Subdural Haematoma</t>
         </is>
       </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Cardiology pool
-Core game</t>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr"/>
@@ -51776,7 +55268,7 @@
           <t>Severe Pre-eclampsia</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E145" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -51867,10 +55359,9 @@
 Posterior Reversible Encephalopathy Syndrome</t>
         </is>
       </c>
-      <c r="E148" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Neurology pool</t>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -51932,7 +55423,7 @@
           <t>Retained Placenta</t>
         </is>
       </c>
-      <c r="E150" s="9" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -51992,7 +55483,7 @@
           <t>Puerperal Sepsis</t>
         </is>
       </c>
-      <c r="E152" s="9" t="inlineStr">
+      <c r="E152" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52022,7 +55513,7 @@
           <t>Shoulder Dystocia</t>
         </is>
       </c>
-      <c r="E153" s="9" t="inlineStr">
+      <c r="E153" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52306,7 +55797,7 @@
           <t>Imperforate Hymen with Haematocolpos</t>
         </is>
       </c>
-      <c r="E162" s="9" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52336,7 +55827,7 @@
           <t>Haemorrhage from Cervical Cancer</t>
         </is>
       </c>
-      <c r="E163" s="9" t="inlineStr">
+      <c r="E163" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52397,7 +55888,7 @@
 Acute Bilirubin Encephalopathy</t>
         </is>
       </c>
-      <c r="E165" s="9" t="inlineStr">
+      <c r="E165" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52431,7 +55922,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E166" s="10" t="inlineStr">
+      <c r="E166" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -52465,7 +55956,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E167" s="10" t="inlineStr">
+      <c r="E167" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -52499,7 +55990,7 @@
           <t>Pelvic Fracture with Haemorrhagic Shock</t>
         </is>
       </c>
-      <c r="E168" s="9" t="inlineStr">
+      <c r="E168" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52561,10 +56052,9 @@
 Gas Gangrene</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr"/>
@@ -52872,7 +56362,7 @@
           <t>Penetrating Abdominal Trauma</t>
         </is>
       </c>
-      <c r="E180" s="9" t="inlineStr">
+      <c r="E180" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -52902,7 +56392,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E181" s="10" t="inlineStr">
+      <c r="E181" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -52968,7 +56458,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E183" s="10" t="inlineStr">
+      <c r="E183" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -53005,10 +56495,9 @@
 Anterior Shoulder Dislocation</t>
         </is>
       </c>
-      <c r="E184" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E184" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr"/>
@@ -53066,7 +56555,7 @@
           <t>Crush Syndrome</t>
         </is>
       </c>
-      <c r="E186" s="9" t="inlineStr">
+      <c r="E186" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53126,7 +56615,7 @@
           <t>Pelvic Fracture with Haemorrhagic Shock</t>
         </is>
       </c>
-      <c r="E188" s="9" t="inlineStr">
+      <c r="E188" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53219,7 +56708,7 @@
           <t>Posterior Urethral Injury</t>
         </is>
       </c>
-      <c r="E191" s="9" t="inlineStr">
+      <c r="E191" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53249,7 +56738,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E192" s="10" t="inlineStr">
+      <c r="E192" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -53316,7 +56805,7 @@
           <t>Flail Chest</t>
         </is>
       </c>
-      <c r="E194" s="9" t="inlineStr">
+      <c r="E194" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53406,7 +56895,7 @@
           <t>Major Burns with Inhalation Injury</t>
         </is>
       </c>
-      <c r="E197" s="9" t="inlineStr">
+      <c r="E197" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53468,10 +56957,9 @@
 Acute Subdural Haematoma</t>
         </is>
       </c>
-      <c r="E199" s="9" t="inlineStr">
-        <is>
-          <t>Added from these documents
-Core game</t>
+      <c r="E199" s="12" t="inlineStr">
+        <is>
+          <t>Added from these documents</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr"/>
@@ -53499,7 +56987,7 @@
           <t>Traumatic Spinal Cord Injury</t>
         </is>
       </c>
-      <c r="E200" s="9" t="inlineStr">
+      <c r="E200" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53561,7 +57049,7 @@
           <t>Hypertrophic Pyloric Stenosis</t>
         </is>
       </c>
-      <c r="E202" s="9" t="inlineStr">
+      <c r="E202" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53594,7 +57082,7 @@
 Oesophageal Atresia with Tracheo-Oesophageal Fistula</t>
         </is>
       </c>
-      <c r="E203" s="9" t="inlineStr">
+      <c r="E203" s="12" t="inlineStr">
         <is>
           <t>Added from these documents</t>
         </is>
@@ -53624,7 +57112,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E204" s="10" t="inlineStr">
+      <c r="E204" s="13" t="inlineStr">
         <is>
           <t>Not in the game</t>
         </is>
@@ -53640,7 +57128,7 @@
   </sheetData>
   <autoFilter ref="A1:H204"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 K2 K3 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 AC2 AC3 AC4 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC35 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AC52 AC53 AC54 AC55 AC56 AC57 AC58 AC59 AC60 AC61 AC62 AC63 AC64 AC65 AC66 AC67 AC68 AC69 AC70 AC71 AC72 AC73 AC74 AC75 AC76 AC77 AC78 AC79 AC80 AC81 AC82 AC83 AC84 AC85 AC86 AC87 AC88 AC89 AC90 AC91 AC92 AC93 AC94 AC95 AC96 AC97 AC98 AC99 AC100 AC101 AC102 AC103 AC104 AC105 AC106 AC107 AC108 AC109 AC110 AC111 AC112 AC113 AC114 AC115 AC116 AC117 AC118 AC119 AC120 AC121 AC122 AC123 AC124 AC125 AC126 AC127 AC128 AC129 AC130 AC131 AC132 AC133 AC134 AC135 AC136 AC137 AC138 AC139 AC140 AC141 AC142 AC143 AC144 AC145 AC146 AC147 AC148 AC149 AC150 AC151 AC152 AC153 AC154 AC155 AC156 AC157 AC158 AC159 AC160 AC161 AC162 AC163 AC164 AC165 AC166 AC167 AC168 AC169 AC170 AC171 AC172 AC173 AC174 AC175 AC176 AC177 AC178 AC179 AC180 AC181 AC182 AC183 AC184 AC185 AC186 AC187 AC188 AC189 AC190 AC191 AC192 AC193 AC194 AC195 AC196 AC197 AC198 AC199 AC200 AC201 AC202 AC203 AC204 AC205 AC206 AC207 AC208 AC209 AC210 AC211 AC212 AC213 AC214 AC215 AC216 AC217 AC218 AC219 AC220 AC221 AC222 AC223 AC224 AC225 AC226 AC227 AC228 AC229 AC230 AC231 AC232 AC233 AC234 AC235 AC236 AC237 AC238 AC239 AC240 AC241 AC242 AC243 AC244 AC245 AC246 AC247 AC248 AC249 AC250 AC251 AC252 AC253 AC254 AC255 AC256 AC257 AC258 AC259 AC260 AC261 AC262 AC263 AC264 AC265 AC266 AC267 AC268 AC269 AC270 AC271 AC272 AC273 AC274 AC275 AC276 AC277 AC278 AC279 AC280 AC281 AC282 AC283 AC284 AC285 AC286 AC287 AC288 AC289 AC290 AC291 AC292 AC293 AC294 AC295 AC296 AC297 AC298 AC299 AC300 AC301 AC302 AC303 AC304 AC305 AC306 AC307 AC308 AC309 AC310 AC311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 AC2 AC3 AC4 AC5 AC6 AC7 AC8 AC9 AC10 AC11 AC12 AC13 AC14 AC15 AC16 AC17 AC18 AC19 AC20 AC21 AC22 AC23 AC24 AC25 AC26 AC27 AC28 AC29 AC30 AC31 AC32 AC33 AC34 AC35 AC36 AC37 AC38 AC39 AC40 AC41 AC42 AC43 AC44 AC45 AC46 AC47 AC48 AC49 AC50 AC51 AC52 AC53 AC54 AC55 AC56 AC57 AC58 AC59 AC60 AC61 AC62 AC63 AC64 AC65 AC66 AC67 AC68 AC69 AC70 AC71 AC72 AC73 AC74 AC75 AC76 AC77 AC78 AC79 AC80 AC81 AC82 AC83 AC84 AC85 AC86 AC87 AC88 AC89 AC90 AC91 AC92 AC93 AC94 AC95 AC96 AC97 AC98 AC99 AC100 AC101 AC102 AC103 AC104 AC105 AC106 AC107 AC108 AC109 AC110 AC111 AC112 AC113 AC114 AC115 AC116 AC117 AC118 AC119 AC120 AC121 AC122 AC123 AC124 AC125 AC126 AC127 AC128 AC129 AC130 AC131 AC132 AC133 AC134 AC135 AC136 AC137 AC138 AC139 AC140 AC141 AC142 AC143 AC144 AC145 AC146 AC147 AC148 AC149 AC150 AC151 AC152 AC153 AC154 AC155 AC156 AC157 AC158 AC159 AC160 AC161 AC162 AC163 AC164 AC165 AC166 AC167 AC168 AC169 AC170 AC171 AC172 AC173 AC174 AC175 AC176 AC177 AC178 AC179 AC180 AC181 AC182 AC183 AC184 AC185 AC186 AC187 AC188 AC189 AC190 AC191 AC192 AC193 AC194 AC195 AC196 AC197 AC198 AC199 AC200 AC201 AC202 AC203 AC204 AC205 AC206 AC207 AC208 AC209 AC210 AC211 AC212 AC213 AC214 AC215 AC216 AC217 AC218 AC219 AC220 AC221 AC222 AC223 AC224 AC225 AC226 AC227 AC228 AC229 AC230 AC231 AC232 AC233 AC234 AC235 AC236 AC237 AC238 AC239 AC240 AC241 AC242 AC243 AC244 AC245 AC246 AC247 AC248 AC249 AC250 AC251 AC252 AC253 AC254 AC255 AC256 AC257 AC258 AC259 AC260 AC261 AC262 AC263 AC264 AC265 AC266 AC267 AC268 AC269 AC270 AC271 AC272 AC273 AC274 AC275 AC276 AC277 AC278 AC279 AC280 AC281 AC282 AC283 AC284 AC285 AC286 AC287 AC288 AC289 AC290 AC291 AC292 AC293 AC294 AC295 AC296 AC297 AC298 AC299 AC300 AC301 AC302 AC303 AC304 AC305 AC306 AC307 AC308 AC309 AC310 AC311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Needs change"</formula1>
     </dataValidation>
   </dataValidations>
